--- a/SAA Biosci Eco_Provisional BOM.xlsx
+++ b/SAA Biosci Eco_Provisional BOM.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{D0A080C9-2597-464D-BAA4-D47914F89801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D8E605D-C30A-4615-8F1E-0EA27AFB7860}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADDA9DD9-DA40-465A-8452-21FFF12F2E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lAMP 6V &amp; 10 MM LENS" sheetId="2" r:id="rId1"/>
@@ -20,15 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -3123,22 +3114,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J286"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="2" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="94.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="38.6640625" style="37" customWidth="1"/>
-    <col min="9" max="9" width="27.109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="10.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="2" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="94.85546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="38.7109375" style="37" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="92" t="s">
         <v>363</v>
       </c>
@@ -3151,7 +3142,7 @@
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
     </row>
-    <row r="2" spans="1:10" s="3" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="3" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
@@ -3183,7 +3174,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -3199,7 +3190,7 @@
       </c>
       <c r="J3" s="12"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -3225,7 +3216,7 @@
       <c r="I4" s="91"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <f t="shared" ref="A5:A17" si="0">A4+1</f>
         <v>2</v>
@@ -3250,7 +3241,7 @@
       <c r="I5" s="91"/>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -3274,7 +3265,7 @@
       <c r="I6" s="91"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3299,7 +3290,7 @@
       <c r="I7" s="91"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>3</v>
       </c>
@@ -3323,7 +3314,7 @@
       <c r="I8" s="91"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3348,7 +3339,7 @@
       <c r="I9" s="91"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>4</v>
       </c>
@@ -3372,7 +3363,7 @@
       <c r="I10" s="91"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3397,7 +3388,7 @@
       <c r="I11" s="91"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>5</v>
       </c>
@@ -3421,7 +3412,7 @@
       <c r="I12" s="91"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3446,7 +3437,7 @@
       <c r="I13" s="91"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>6</v>
       </c>
@@ -3470,7 +3461,7 @@
       <c r="I14" s="91"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3495,7 +3486,7 @@
       <c r="I15" s="91"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>7</v>
       </c>
@@ -3519,7 +3510,7 @@
       <c r="I16" s="91"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3544,7 +3535,7 @@
       <c r="I17" s="91"/>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>8</v>
       </c>
@@ -3568,7 +3559,7 @@
       <c r="I18" s="55"/>
       <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="4"/>
       <c r="C19" s="6"/>
@@ -3580,7 +3571,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>10</v>
       </c>
@@ -3594,7 +3585,7 @@
       <c r="I20" s="11"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>1</v>
       </c>
@@ -3622,7 +3613,7 @@
       </c>
       <c r="J21" s="5"/>
     </row>
-    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>2</v>
       </c>
@@ -3646,7 +3637,7 @@
       <c r="I22" s="104"/>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>3</v>
       </c>
@@ -3670,7 +3661,7 @@
       <c r="I23" s="104"/>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -3694,7 +3685,7 @@
       <c r="I24" s="104"/>
       <c r="J24" s="5"/>
     </row>
-    <row r="25" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>5</v>
       </c>
@@ -3718,7 +3709,7 @@
       <c r="I25" s="104"/>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>6</v>
       </c>
@@ -3742,7 +3733,7 @@
       <c r="I26" s="104"/>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>7</v>
       </c>
@@ -3766,7 +3757,7 @@
       <c r="I27" s="104"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>8</v>
       </c>
@@ -3790,7 +3781,7 @@
       <c r="I28" s="104"/>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>9</v>
       </c>
@@ -3814,7 +3805,7 @@
       <c r="I29" s="105"/>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>10</v>
       </c>
@@ -3838,7 +3829,7 @@
       <c r="I30" s="9"/>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="9"/>
@@ -3850,7 +3841,7 @@
       <c r="I31" s="9"/>
       <c r="J31" s="5"/>
     </row>
-    <row r="32" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>11</v>
       </c>
@@ -3864,7 +3855,7 @@
       <c r="I32" s="11"/>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1</v>
       </c>
@@ -3890,9 +3881,11 @@
       <c r="I33" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="J33" s="5"/>
-    </row>
-    <row r="34" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J33" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>2</v>
       </c>
@@ -3918,9 +3911,11 @@
       <c r="I34" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="J34" s="5"/>
-    </row>
-    <row r="35" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J34" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
         <v>3</v>
       </c>
@@ -3948,7 +3943,7 @@
       </c>
       <c r="J35" s="15"/>
     </row>
-    <row r="36" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>4</v>
       </c>
@@ -3974,7 +3969,7 @@
       <c r="I36" s="9"/>
       <c r="J36" s="5"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>5</v>
       </c>
@@ -4002,7 +3997,7 @@
       </c>
       <c r="J37" s="5"/>
     </row>
-    <row r="38" spans="1:10" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>7</v>
       </c>
@@ -4032,7 +4027,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>8</v>
       </c>
@@ -4060,7 +4055,7 @@
       </c>
       <c r="J39" s="5"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>9</v>
       </c>
@@ -4084,7 +4079,7 @@
       </c>
       <c r="J40" s="5"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>10</v>
       </c>
@@ -4108,7 +4103,7 @@
       </c>
       <c r="J41" s="5"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -4120,7 +4115,7 @@
       <c r="I42" s="9"/>
       <c r="J42" s="5"/>
     </row>
-    <row r="43" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
         <v>24</v>
       </c>
@@ -4134,7 +4129,7 @@
       <c r="I43" s="11"/>
       <c r="J43" s="12"/>
     </row>
-    <row r="44" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
         <v>1</v>
       </c>
@@ -4162,7 +4157,7 @@
       </c>
       <c r="J44" s="15"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <f>A44+1</f>
         <v>2</v>
@@ -4191,7 +4186,7 @@
       </c>
       <c r="J45" s="12"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>3</v>
       </c>
@@ -4219,7 +4214,7 @@
       </c>
       <c r="J46" s="12"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>4</v>
       </c>
@@ -4247,7 +4242,7 @@
       </c>
       <c r="J47" s="12"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -4261,7 +4256,7 @@
       </c>
       <c r="J48" s="5"/>
     </row>
-    <row r="49" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
         <v>27</v>
       </c>
@@ -4275,7 +4270,7 @@
       <c r="I49" s="11"/>
       <c r="J49" s="12"/>
     </row>
-    <row r="50" spans="1:10" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A50" s="18"/>
       <c r="B50" s="68" t="s">
         <v>476</v>
@@ -4293,7 +4288,7 @@
       <c r="I50" s="11"/>
       <c r="J50" s="12"/>
     </row>
-    <row r="51" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="18">
         <v>1</v>
       </c>
@@ -4321,7 +4316,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="18"/>
       <c r="B52" s="67" t="s">
         <v>462</v>
@@ -4347,7 +4342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="18"/>
       <c r="B53" s="67" t="s">
         <v>463</v>
@@ -4373,7 +4368,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="18"/>
       <c r="B54" s="85" t="s">
         <v>464</v>
@@ -4399,7 +4394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="18"/>
       <c r="B55" s="85" t="s">
         <v>465</v>
@@ -4425,7 +4420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="18"/>
       <c r="B56" s="67" t="s">
         <v>466</v>
@@ -4451,7 +4446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="18"/>
       <c r="B57" s="67" t="s">
         <v>467</v>
@@ -4477,7 +4472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="18"/>
       <c r="B58" s="67" t="s">
         <v>468</v>
@@ -4503,7 +4498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="18"/>
       <c r="B59" s="67" t="s">
         <v>469</v>
@@ -4527,7 +4522,7 @@
       <c r="I59" s="11"/>
       <c r="J59" s="12"/>
     </row>
-    <row r="60" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -4539,7 +4534,7 @@
       <c r="I60" s="11"/>
       <c r="J60" s="12"/>
     </row>
-    <row r="61" spans="1:10" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A61" s="18"/>
       <c r="B61" s="68" t="s">
         <v>477</v>
@@ -4557,7 +4552,7 @@
       <c r="I61" s="11"/>
       <c r="J61" s="12"/>
     </row>
-    <row r="62" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="18"/>
       <c r="B62" s="67" t="s">
         <v>470</v>
@@ -4583,7 +4578,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="18"/>
       <c r="B63" s="67" t="s">
         <v>471</v>
@@ -4609,7 +4604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="18"/>
       <c r="B64" s="67" t="s">
         <v>472</v>
@@ -4635,7 +4630,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="18"/>
       <c r="B65" s="67" t="s">
         <v>473</v>
@@ -4661,7 +4656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="18"/>
       <c r="B66" s="67" t="s">
         <v>474</v>
@@ -4687,7 +4682,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="18"/>
       <c r="B67" s="67" t="s">
         <v>475</v>
@@ -4711,7 +4706,7 @@
       <c r="I67" s="11"/>
       <c r="J67" s="12"/>
     </row>
-    <row r="68" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="18"/>
       <c r="B68" s="67" t="s">
         <v>192</v>
@@ -4737,7 +4732,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="18"/>
       <c r="B69" s="67" t="s">
         <v>191</v>
@@ -4761,7 +4756,7 @@
       <c r="I69" s="11"/>
       <c r="J69" s="12"/>
     </row>
-    <row r="70" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="18"/>
       <c r="B70" s="18"/>
       <c r="C70" s="18"/>
@@ -4773,7 +4768,7 @@
       <c r="I70" s="11"/>
       <c r="J70" s="12"/>
     </row>
-    <row r="71" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="18"/>
       <c r="B71" s="15" t="s">
         <v>193</v>
@@ -4793,7 +4788,7 @@
       <c r="I71" s="11"/>
       <c r="J71" s="12"/>
     </row>
-    <row r="72" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
       <c r="B72" s="15" t="s">
         <v>194</v>
@@ -4823,7 +4818,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
       <c r="B73" s="15" t="s">
         <v>195</v>
@@ -4853,7 +4848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="18"/>
       <c r="B74" s="15" t="s">
         <v>196</v>
@@ -4883,7 +4878,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
@@ -4895,7 +4890,7 @@
       <c r="I75" s="12"/>
       <c r="J75" s="12"/>
     </row>
-    <row r="76" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
       <c r="B76" s="15" t="s">
         <v>197</v>
@@ -4915,7 +4910,7 @@
       <c r="I76" s="12"/>
       <c r="J76" s="12"/>
     </row>
-    <row r="77" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="15"/>
       <c r="B77" s="15" t="s">
         <v>198</v>
@@ -4945,7 +4940,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:10" s="10" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" s="10" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A78" s="18"/>
       <c r="B78" s="15" t="s">
         <v>199</v>
@@ -4975,7 +4970,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="79" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
       <c r="B79" s="15" t="s">
         <v>200</v>
@@ -5005,7 +5000,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="80" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
       <c r="B80" s="15" t="s">
         <v>201</v>
@@ -5035,7 +5030,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="81" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
       <c r="B81" s="15" t="s">
         <v>202</v>
@@ -5063,7 +5058,7 @@
       </c>
       <c r="J81" s="12"/>
     </row>
-    <row r="82" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="18"/>
       <c r="B82" s="15" t="s">
         <v>203</v>
@@ -5093,7 +5088,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="83" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="18"/>
       <c r="B83" s="15" t="s">
         <v>330</v>
@@ -5121,7 +5116,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="84" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="15"/>
       <c r="B84" s="15" t="s">
         <v>333</v>
@@ -5147,7 +5142,7 @@
       </c>
       <c r="J84" s="15"/>
     </row>
-    <row r="85" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="18"/>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -5159,7 +5154,7 @@
       <c r="I85" s="12"/>
       <c r="J85" s="12"/>
     </row>
-    <row r="86" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="18"/>
       <c r="B86" s="15" t="s">
         <v>204</v>
@@ -5179,7 +5174,7 @@
       <c r="I86" s="12"/>
       <c r="J86" s="12"/>
     </row>
-    <row r="87" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="18"/>
       <c r="B87" s="15" t="s">
         <v>205</v>
@@ -5209,7 +5204,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="88" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="18"/>
       <c r="B88" s="15" t="s">
         <v>206</v>
@@ -5239,7 +5234,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="89" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="18"/>
       <c r="B89" s="15" t="s">
         <v>207</v>
@@ -5269,7 +5264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="18"/>
       <c r="B90" s="15" t="s">
         <v>208</v>
@@ -5299,7 +5294,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="18"/>
       <c r="B91" s="15" t="s">
         <v>349</v>
@@ -5323,7 +5318,7 @@
       <c r="I91" s="11"/>
       <c r="J91" s="12"/>
     </row>
-    <row r="92" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="18"/>
       <c r="B92" s="15" t="s">
         <v>350</v>
@@ -5347,7 +5342,7 @@
       <c r="I92" s="11"/>
       <c r="J92" s="12"/>
     </row>
-    <row r="93" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="18"/>
       <c r="B93" s="15" t="s">
         <v>351</v>
@@ -5371,7 +5366,7 @@
       <c r="I93" s="11"/>
       <c r="J93" s="12"/>
     </row>
-    <row r="94" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="18"/>
       <c r="B94" s="15" t="s">
         <v>352</v>
@@ -5395,7 +5390,7 @@
       <c r="I94" s="11"/>
       <c r="J94" s="12"/>
     </row>
-    <row r="95" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="18"/>
       <c r="B95" s="18"/>
       <c r="C95" s="18"/>
@@ -5407,7 +5402,7 @@
       <c r="I95" s="11"/>
       <c r="J95" s="12"/>
     </row>
-    <row r="96" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="18"/>
       <c r="B96" s="15" t="s">
         <v>209</v>
@@ -5429,7 +5424,7 @@
       <c r="I96" s="11"/>
       <c r="J96" s="12"/>
     </row>
-    <row r="97" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="18"/>
       <c r="B97" s="15" t="s">
         <v>210</v>
@@ -5459,7 +5454,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:10" s="16" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" s="16" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="15"/>
       <c r="B98" s="15" t="s">
         <v>211</v>
@@ -5487,7 +5482,7 @@
       </c>
       <c r="J98" s="15"/>
     </row>
-    <row r="99" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="18"/>
       <c r="B99" s="18"/>
       <c r="C99" s="15"/>
@@ -5499,7 +5494,7 @@
       <c r="I99" s="12"/>
       <c r="J99" s="12"/>
     </row>
-    <row r="100" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="18"/>
       <c r="B100" s="15" t="s">
         <v>212</v>
@@ -5519,7 +5514,7 @@
       <c r="I100" s="12"/>
       <c r="J100" s="12"/>
     </row>
-    <row r="101" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="18"/>
       <c r="B101" s="15" t="s">
         <v>213</v>
@@ -5549,7 +5544,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="102" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="18"/>
       <c r="B102" s="15" t="s">
         <v>214</v>
@@ -5579,7 +5574,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="103" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="18"/>
       <c r="B103" s="15" t="s">
         <v>215</v>
@@ -5609,7 +5604,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="104" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="18"/>
       <c r="B104" s="15"/>
       <c r="C104" s="18"/>
@@ -5621,7 +5616,7 @@
       <c r="I104" s="12"/>
       <c r="J104" s="12"/>
     </row>
-    <row r="105" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="18"/>
       <c r="B105" s="15" t="s">
         <v>216</v>
@@ -5639,7 +5634,7 @@
       <c r="I105" s="12"/>
       <c r="J105" s="12"/>
     </row>
-    <row r="106" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="18"/>
       <c r="B106" s="15" t="s">
         <v>217</v>
@@ -5669,7 +5664,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="107" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="18"/>
       <c r="B107" s="15" t="s">
         <v>218</v>
@@ -5699,7 +5694,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="108" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="15"/>
       <c r="B108" s="15" t="s">
         <v>219</v>
@@ -5727,7 +5722,7 @@
       </c>
       <c r="J108" s="15"/>
     </row>
-    <row r="109" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="15"/>
       <c r="B109" s="15" t="s">
         <v>220</v>
@@ -5755,7 +5750,7 @@
       </c>
       <c r="J109" s="15"/>
     </row>
-    <row r="110" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="18"/>
       <c r="B110" s="18"/>
       <c r="C110" s="15"/>
@@ -5767,7 +5762,7 @@
       <c r="I110" s="12"/>
       <c r="J110" s="12"/>
     </row>
-    <row r="111" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="18" t="s">
         <v>58</v>
       </c>
@@ -5781,7 +5776,7 @@
       <c r="I111" s="15"/>
       <c r="J111" s="15"/>
     </row>
-    <row r="112" spans="1:10" s="16" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" s="16" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="15">
         <v>1</v>
       </c>
@@ -5811,7 +5806,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>2</v>
       </c>
@@ -5841,7 +5836,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="15">
         <v>3</v>
       </c>
@@ -5869,7 +5864,7 @@
       </c>
       <c r="J114" s="5"/>
     </row>
-    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>4</v>
       </c>
@@ -5897,7 +5892,7 @@
       </c>
       <c r="J115" s="5"/>
     </row>
-    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="15">
         <v>5</v>
       </c>
@@ -5925,7 +5920,7 @@
       </c>
       <c r="J116" s="5"/>
     </row>
-    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>6</v>
       </c>
@@ -5953,7 +5948,7 @@
       </c>
       <c r="J117" s="5"/>
     </row>
-    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="15">
         <v>7</v>
       </c>
@@ -5981,7 +5976,7 @@
       </c>
       <c r="J118" s="5"/>
     </row>
-    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>8</v>
       </c>
@@ -6009,7 +6004,7 @@
       </c>
       <c r="J119" s="5"/>
     </row>
-    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="15">
         <v>9</v>
       </c>
@@ -6039,7 +6034,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" ht="32.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>10</v>
       </c>
@@ -6069,7 +6064,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="32.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" ht="32.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>11</v>
       </c>
@@ -6095,7 +6090,7 @@
       <c r="I122" s="12"/>
       <c r="J122" s="12"/>
     </row>
-    <row r="123" spans="1:10" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A123" s="15">
         <v>12</v>
       </c>
@@ -6125,7 +6120,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>13</v>
       </c>
@@ -6147,7 +6142,7 @@
       <c r="I124" s="12"/>
       <c r="J124" s="5"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>14</v>
       </c>
@@ -6177,7 +6172,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="15">
         <v>15</v>
       </c>
@@ -6207,7 +6202,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>16</v>
       </c>
@@ -6235,7 +6230,7 @@
       </c>
       <c r="J127" s="12"/>
     </row>
-    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>17</v>
       </c>
@@ -6265,7 +6260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="15">
         <v>18</v>
       </c>
@@ -6291,7 +6286,7 @@
       <c r="I129" s="12"/>
       <c r="J129" s="5"/>
     </row>
-    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>19</v>
       </c>
@@ -6319,7 +6314,7 @@
       </c>
       <c r="J130" s="5"/>
     </row>
-    <row r="131" spans="1:10" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>20</v>
       </c>
@@ -6345,7 +6340,7 @@
       </c>
       <c r="J131" s="5"/>
     </row>
-    <row r="132" spans="1:10" s="16" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" s="16" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="15">
         <v>21</v>
       </c>
@@ -6375,7 +6370,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>22</v>
       </c>
@@ -6403,7 +6398,7 @@
       </c>
       <c r="J133" s="5"/>
     </row>
-    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="5">
         <v>23</v>
       </c>
@@ -6433,7 +6428,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="15">
         <v>24</v>
       </c>
@@ -6459,7 +6454,7 @@
       <c r="I135" s="12"/>
       <c r="J135" s="5"/>
     </row>
-    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="5">
         <v>25</v>
       </c>
@@ -6485,7 +6480,7 @@
       <c r="I136" s="12"/>
       <c r="J136" s="5"/>
     </row>
-    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="5">
         <v>26</v>
       </c>
@@ -6511,7 +6506,7 @@
       <c r="I137" s="12"/>
       <c r="J137" s="5"/>
     </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -6523,7 +6518,7 @@
       <c r="I138" s="12"/>
       <c r="J138" s="5"/>
     </row>
-    <row r="139" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A139" s="18" t="s">
         <v>83</v>
       </c>
@@ -6536,7 +6531,7 @@
       <c r="I139" s="12"/>
       <c r="J139" s="12"/>
     </row>
-    <row r="140" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>1</v>
       </c>
@@ -6562,7 +6557,7 @@
       </c>
       <c r="J140" s="5"/>
     </row>
-    <row r="141" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="5">
         <v>3</v>
       </c>
@@ -6588,7 +6583,7 @@
       </c>
       <c r="J141" s="5"/>
     </row>
-    <row r="142" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="5">
         <v>4</v>
       </c>
@@ -6614,7 +6609,7 @@
       </c>
       <c r="J142" s="5"/>
     </row>
-    <row r="143" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="5">
         <v>5</v>
       </c>
@@ -6640,7 +6635,7 @@
       </c>
       <c r="J143" s="5"/>
     </row>
-    <row r="144" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="5">
         <v>6</v>
       </c>
@@ -6666,7 +6661,7 @@
       </c>
       <c r="J144" s="5"/>
     </row>
-    <row r="145" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="5">
         <v>7</v>
       </c>
@@ -6692,7 +6687,7 @@
       </c>
       <c r="J145" s="5"/>
     </row>
-    <row r="146" spans="1:10" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <v>8</v>
       </c>
@@ -6718,7 +6713,7 @@
       </c>
       <c r="J146" s="5"/>
     </row>
-    <row r="147" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A147" s="15"/>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
@@ -6730,7 +6725,7 @@
       <c r="I147" s="60"/>
       <c r="J147" s="15"/>
     </row>
-    <row r="148" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A148" s="18" t="s">
         <v>84</v>
       </c>
@@ -6746,7 +6741,7 @@
       <c r="I148" s="17"/>
       <c r="J148" s="15"/>
     </row>
-    <row r="149" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="27">
         <v>1</v>
       </c>
@@ -6774,7 +6769,7 @@
       </c>
       <c r="J149" s="5"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="27">
         <v>2</v>
       </c>
@@ -6798,7 +6793,7 @@
       <c r="I150" s="101"/>
       <c r="J150" s="5"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="27">
         <v>3</v>
       </c>
@@ -6822,7 +6817,7 @@
       <c r="I151" s="101"/>
       <c r="J151" s="5"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="27">
         <v>4</v>
       </c>
@@ -6846,7 +6841,7 @@
       <c r="I152" s="101"/>
       <c r="J152" s="5"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="27">
         <v>5</v>
       </c>
@@ -6870,7 +6865,7 @@
       <c r="I153" s="101"/>
       <c r="J153" s="5"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="27">
         <v>6</v>
       </c>
@@ -6894,7 +6889,7 @@
       <c r="I154" s="101"/>
       <c r="J154" s="5"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="27">
         <v>7</v>
       </c>
@@ -6918,7 +6913,7 @@
       <c r="I155" s="101"/>
       <c r="J155" s="5"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="27">
         <v>8</v>
       </c>
@@ -6942,7 +6937,7 @@
       <c r="I156" s="101"/>
       <c r="J156" s="5"/>
     </row>
-    <row r="157" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="27">
         <v>9</v>
       </c>
@@ -6966,7 +6961,7 @@
       <c r="I157" s="101"/>
       <c r="J157" s="5"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="27">
         <v>10</v>
       </c>
@@ -6990,7 +6985,7 @@
       <c r="I158" s="101"/>
       <c r="J158" s="5"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="27">
         <v>11</v>
       </c>
@@ -7014,7 +7009,7 @@
       <c r="I159" s="101"/>
       <c r="J159" s="5"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" s="27">
         <v>12</v>
       </c>
@@ -7038,7 +7033,7 @@
       <c r="I160" s="101"/>
       <c r="J160" s="5"/>
     </row>
-    <row r="161" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A161" s="27">
         <v>13</v>
       </c>
@@ -7062,7 +7057,7 @@
       <c r="I161" s="101"/>
       <c r="J161" s="15"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" s="27">
         <v>14</v>
       </c>
@@ -7086,7 +7081,7 @@
       <c r="I162" s="101"/>
       <c r="J162" s="5"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="27">
         <v>15</v>
       </c>
@@ -7110,7 +7105,7 @@
       <c r="I163" s="101"/>
       <c r="J163" s="5"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="27">
         <v>16</v>
       </c>
@@ -7134,7 +7129,7 @@
       <c r="I164" s="101"/>
       <c r="J164" s="5"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" s="27">
         <v>17</v>
       </c>
@@ -7158,7 +7153,7 @@
       <c r="I165" s="101"/>
       <c r="J165" s="5"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" s="27">
         <v>18</v>
       </c>
@@ -7182,7 +7177,7 @@
       <c r="I166" s="101"/>
       <c r="J166" s="5"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" s="27">
         <v>19</v>
       </c>
@@ -7206,7 +7201,7 @@
       <c r="I167" s="101"/>
       <c r="J167" s="5"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" s="27">
         <v>20</v>
       </c>
@@ -7230,7 +7225,7 @@
       <c r="I168" s="101"/>
       <c r="J168" s="5"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" s="27">
         <v>21</v>
       </c>
@@ -7254,7 +7249,7 @@
       <c r="I169" s="101"/>
       <c r="J169" s="5"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="27">
         <v>22</v>
       </c>
@@ -7278,7 +7273,7 @@
       <c r="I170" s="101"/>
       <c r="J170" s="5"/>
     </row>
-    <row r="171" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A171" s="27">
         <v>23</v>
       </c>
@@ -7302,7 +7297,7 @@
       <c r="I171" s="101"/>
       <c r="J171" s="5"/>
     </row>
-    <row r="172" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A172" s="27">
         <v>24</v>
       </c>
@@ -7326,7 +7321,7 @@
       <c r="I172" s="102"/>
       <c r="J172" s="15"/>
     </row>
-    <row r="173" spans="1:10" s="16" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" s="16" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="27">
         <v>25</v>
       </c>
@@ -7352,7 +7347,7 @@
       <c r="I173" s="62"/>
       <c r="J173" s="15"/>
     </row>
-    <row r="174" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A174" s="27">
         <v>26</v>
       </c>
@@ -7378,7 +7373,7 @@
       </c>
       <c r="J174" s="15"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" s="27"/>
       <c r="C175" s="31"/>
       <c r="D175" s="5"/>
@@ -7389,7 +7384,7 @@
       <c r="I175" s="9"/>
       <c r="J175" s="5"/>
     </row>
-    <row r="176" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A176" s="18" t="s">
         <v>111</v>
       </c>
@@ -7403,7 +7398,7 @@
       <c r="I176" s="17"/>
       <c r="J176" s="15"/>
     </row>
-    <row r="177" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A177" s="18"/>
       <c r="B177" s="58" t="s">
         <v>478</v>
@@ -7421,7 +7416,7 @@
       <c r="I177" s="17"/>
       <c r="J177" s="15"/>
     </row>
-    <row r="178" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A178" s="18"/>
       <c r="B178" s="58" t="s">
         <v>479</v>
@@ -7443,7 +7438,7 @@
       <c r="I178" s="17"/>
       <c r="J178" s="15"/>
     </row>
-    <row r="179" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A179" s="18"/>
       <c r="B179" s="58" t="s">
         <v>480</v>
@@ -7465,7 +7460,7 @@
       <c r="I179" s="17"/>
       <c r="J179" s="15"/>
     </row>
-    <row r="180" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A180" s="18"/>
       <c r="B180" s="58" t="s">
         <v>488</v>
@@ -7487,7 +7482,7 @@
       <c r="I180" s="17"/>
       <c r="J180" s="15"/>
     </row>
-    <row r="181" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A181" s="18"/>
       <c r="B181" s="58" t="s">
         <v>489</v>
@@ -7509,7 +7504,7 @@
       <c r="I181" s="17"/>
       <c r="J181" s="15"/>
     </row>
-    <row r="182" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A182" s="18"/>
       <c r="B182" s="18"/>
       <c r="C182" s="18"/>
@@ -7521,7 +7516,7 @@
       <c r="I182" s="17"/>
       <c r="J182" s="15"/>
     </row>
-    <row r="183" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" s="16" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A183" s="18" t="s">
         <v>113</v>
       </c>
@@ -7535,7 +7530,7 @@
       <c r="I183" s="17"/>
       <c r="J183" s="15"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="5">
         <v>1</v>
       </c>
@@ -7557,7 +7552,7 @@
       <c r="I184" s="9"/>
       <c r="J184" s="5"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="5">
         <v>2</v>
       </c>
@@ -7579,7 +7574,7 @@
       <c r="I185" s="9"/>
       <c r="J185" s="5"/>
     </row>
-    <row r="186" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="5">
         <v>3</v>
       </c>
@@ -7601,7 +7596,7 @@
       <c r="I186" s="9"/>
       <c r="J186" s="5"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="5">
         <v>4</v>
       </c>
@@ -7623,7 +7618,7 @@
       <c r="I187" s="9"/>
       <c r="J187" s="5"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <v>5</v>
       </c>
@@ -7645,7 +7640,7 @@
       <c r="I188" s="9"/>
       <c r="J188" s="5"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A189" s="5">
         <v>6</v>
       </c>
@@ -7665,7 +7660,7 @@
       <c r="I189" s="9"/>
       <c r="J189" s="5"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="5">
         <v>7</v>
       </c>
@@ -7687,7 +7682,7 @@
       <c r="I190" s="9"/>
       <c r="J190" s="5"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="5">
         <v>8</v>
       </c>
@@ -7709,7 +7704,7 @@
       <c r="I191" s="9"/>
       <c r="J191" s="5"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
         <v>9</v>
       </c>
@@ -7731,7 +7726,7 @@
       <c r="I192" s="9"/>
       <c r="J192" s="5"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="5">
         <v>10</v>
       </c>
@@ -7753,7 +7748,7 @@
       <c r="I193" s="9"/>
       <c r="J193" s="5"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="5">
         <v>11</v>
       </c>
@@ -7775,7 +7770,7 @@
       <c r="I194" s="9"/>
       <c r="J194" s="5"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="5">
         <v>12</v>
       </c>
@@ -7797,7 +7792,7 @@
       <c r="I195" s="9"/>
       <c r="J195" s="5"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="5">
         <v>13</v>
       </c>
@@ -7819,7 +7814,7 @@
       <c r="I196" s="9"/>
       <c r="J196" s="5"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="5">
         <v>14</v>
       </c>
@@ -7841,7 +7836,7 @@
       <c r="I197" s="9"/>
       <c r="J197" s="5"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="5">
         <v>15</v>
       </c>
@@ -7863,7 +7858,7 @@
       <c r="I198" s="9"/>
       <c r="J198" s="5"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="5">
         <v>16</v>
       </c>
@@ -7885,7 +7880,7 @@
       <c r="I199" s="9"/>
       <c r="J199" s="5"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="5">
         <v>17</v>
       </c>
@@ -7907,7 +7902,7 @@
       <c r="I200" s="9"/>
       <c r="J200" s="5"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="5">
         <v>18</v>
       </c>
@@ -7929,7 +7924,7 @@
       <c r="I201" s="70"/>
       <c r="J201" s="5"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="5">
         <v>19</v>
       </c>
@@ -7947,7 +7942,7 @@
       </c>
       <c r="H202" s="20"/>
     </row>
-    <row r="205" spans="1:10" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="98" t="s">
         <v>280</v>
       </c>
@@ -7962,7 +7957,7 @@
       <c r="H205" s="39"/>
       <c r="J205" s="21"/>
     </row>
-    <row r="208" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7971,7 +7966,7 @@
       <c r="H208" s="37"/>
       <c r="I208" s="1"/>
     </row>
-    <row r="209" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7980,7 +7975,7 @@
       <c r="H209" s="37"/>
       <c r="I209" s="1"/>
     </row>
-    <row r="210" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7989,7 +7984,7 @@
       <c r="H210" s="37"/>
       <c r="I210" s="1"/>
     </row>
-    <row r="211" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7998,7 +7993,7 @@
       <c r="H211" s="37"/>
       <c r="I211" s="1"/>
     </row>
-    <row r="212" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -8007,7 +8002,7 @@
       <c r="H212" s="37"/>
       <c r="I212" s="1"/>
     </row>
-    <row r="213" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -8016,7 +8011,7 @@
       <c r="H213" s="37"/>
       <c r="I213" s="1"/>
     </row>
-    <row r="214" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -8025,7 +8020,7 @@
       <c r="H214" s="37"/>
       <c r="I214" s="1"/>
     </row>
-    <row r="215" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -8034,7 +8029,7 @@
       <c r="H215" s="37"/>
       <c r="I215" s="1"/>
     </row>
-    <row r="216" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -8043,7 +8038,7 @@
       <c r="H216" s="37"/>
       <c r="I216" s="1"/>
     </row>
-    <row r="217" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -8052,7 +8047,7 @@
       <c r="H217" s="37"/>
       <c r="I217" s="1"/>
     </row>
-    <row r="218" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -8061,7 +8056,7 @@
       <c r="H218" s="37"/>
       <c r="I218" s="1"/>
     </row>
-    <row r="219" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -8070,7 +8065,7 @@
       <c r="H219" s="37"/>
       <c r="I219" s="1"/>
     </row>
-    <row r="220" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -8079,7 +8074,7 @@
       <c r="H220" s="37"/>
       <c r="I220" s="1"/>
     </row>
-    <row r="221" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -8088,7 +8083,7 @@
       <c r="H221" s="37"/>
       <c r="I221" s="1"/>
     </row>
-    <row r="222" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -8097,7 +8092,7 @@
       <c r="H222" s="37"/>
       <c r="I222" s="1"/>
     </row>
-    <row r="223" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -8106,7 +8101,7 @@
       <c r="H223" s="37"/>
       <c r="I223" s="1"/>
     </row>
-    <row r="224" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -8115,7 +8110,7 @@
       <c r="H224" s="37"/>
       <c r="I224" s="1"/>
     </row>
-    <row r="225" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -8124,7 +8119,7 @@
       <c r="H225" s="37"/>
       <c r="I225" s="1"/>
     </row>
-    <row r="226" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -8133,7 +8128,7 @@
       <c r="H226" s="37"/>
       <c r="I226" s="1"/>
     </row>
-    <row r="227" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -8142,7 +8137,7 @@
       <c r="H227" s="37"/>
       <c r="I227" s="1"/>
     </row>
-    <row r="228" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -8151,7 +8146,7 @@
       <c r="H228" s="37"/>
       <c r="I228" s="1"/>
     </row>
-    <row r="229" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -8160,7 +8155,7 @@
       <c r="H229" s="37"/>
       <c r="I229" s="1"/>
     </row>
-    <row r="230" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -8169,7 +8164,7 @@
       <c r="H230" s="37"/>
       <c r="I230" s="1"/>
     </row>
-    <row r="231" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -8178,7 +8173,7 @@
       <c r="H231" s="37"/>
       <c r="I231" s="1"/>
     </row>
-    <row r="232" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -8187,7 +8182,7 @@
       <c r="H232" s="37"/>
       <c r="I232" s="1"/>
     </row>
-    <row r="233" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -8196,7 +8191,7 @@
       <c r="H233" s="37"/>
       <c r="I233" s="1"/>
     </row>
-    <row r="234" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8205,7 +8200,7 @@
       <c r="H234" s="37"/>
       <c r="I234" s="1"/>
     </row>
-    <row r="235" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8214,7 +8209,7 @@
       <c r="H235" s="37"/>
       <c r="I235" s="1"/>
     </row>
-    <row r="236" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8223,7 +8218,7 @@
       <c r="H236" s="37"/>
       <c r="I236" s="1"/>
     </row>
-    <row r="237" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8232,7 +8227,7 @@
       <c r="H237" s="37"/>
       <c r="I237" s="1"/>
     </row>
-    <row r="238" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8241,7 +8236,7 @@
       <c r="H238" s="37"/>
       <c r="I238" s="1"/>
     </row>
-    <row r="239" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8250,7 +8245,7 @@
       <c r="H239" s="37"/>
       <c r="I239" s="1"/>
     </row>
-    <row r="240" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8259,7 +8254,7 @@
       <c r="H240" s="37"/>
       <c r="I240" s="1"/>
     </row>
-    <row r="241" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8268,7 +8263,7 @@
       <c r="H241" s="37"/>
       <c r="I241" s="1"/>
     </row>
-    <row r="242" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8277,7 +8272,7 @@
       <c r="H242" s="37"/>
       <c r="I242" s="1"/>
     </row>
-    <row r="243" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8286,7 +8281,7 @@
       <c r="H243" s="37"/>
       <c r="I243" s="1"/>
     </row>
-    <row r="244" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8295,7 +8290,7 @@
       <c r="H244" s="37"/>
       <c r="I244" s="1"/>
     </row>
-    <row r="245" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8304,7 +8299,7 @@
       <c r="H245" s="37"/>
       <c r="I245" s="1"/>
     </row>
-    <row r="246" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8313,7 +8308,7 @@
       <c r="H246" s="37"/>
       <c r="I246" s="1"/>
     </row>
-    <row r="247" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8322,7 +8317,7 @@
       <c r="H247" s="37"/>
       <c r="I247" s="1"/>
     </row>
-    <row r="248" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8331,7 +8326,7 @@
       <c r="H248" s="37"/>
       <c r="I248" s="1"/>
     </row>
-    <row r="249" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8340,7 +8335,7 @@
       <c r="H249" s="37"/>
       <c r="I249" s="1"/>
     </row>
-    <row r="250" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8349,7 +8344,7 @@
       <c r="H250" s="37"/>
       <c r="I250" s="1"/>
     </row>
-    <row r="251" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8358,7 +8353,7 @@
       <c r="H251" s="37"/>
       <c r="I251" s="1"/>
     </row>
-    <row r="252" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8367,7 +8362,7 @@
       <c r="H252" s="37"/>
       <c r="I252" s="1"/>
     </row>
-    <row r="253" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8376,7 +8371,7 @@
       <c r="H253" s="37"/>
       <c r="I253" s="1"/>
     </row>
-    <row r="254" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -8385,7 +8380,7 @@
       <c r="H254" s="37"/>
       <c r="I254" s="1"/>
     </row>
-    <row r="255" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -8394,7 +8389,7 @@
       <c r="H255" s="37"/>
       <c r="I255" s="1"/>
     </row>
-    <row r="256" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -8403,7 +8398,7 @@
       <c r="H256" s="37"/>
       <c r="I256" s="1"/>
     </row>
-    <row r="257" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -8412,7 +8407,7 @@
       <c r="H257" s="37"/>
       <c r="I257" s="1"/>
     </row>
-    <row r="258" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -8421,7 +8416,7 @@
       <c r="H258" s="37"/>
       <c r="I258" s="1"/>
     </row>
-    <row r="259" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -8430,7 +8425,7 @@
       <c r="H259" s="37"/>
       <c r="I259" s="1"/>
     </row>
-    <row r="260" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -8439,7 +8434,7 @@
       <c r="H260" s="37"/>
       <c r="I260" s="1"/>
     </row>
-    <row r="261" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -8448,7 +8443,7 @@
       <c r="H261" s="37"/>
       <c r="I261" s="1"/>
     </row>
-    <row r="262" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -8457,7 +8452,7 @@
       <c r="H262" s="37"/>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -8466,7 +8461,7 @@
       <c r="H263" s="37"/>
       <c r="I263" s="1"/>
     </row>
-    <row r="264" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -8475,7 +8470,7 @@
       <c r="H264" s="37"/>
       <c r="I264" s="1"/>
     </row>
-    <row r="265" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -8484,7 +8479,7 @@
       <c r="H265" s="37"/>
       <c r="I265" s="1"/>
     </row>
-    <row r="266" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -8493,7 +8488,7 @@
       <c r="H266" s="37"/>
       <c r="I266" s="1"/>
     </row>
-    <row r="267" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -8502,7 +8497,7 @@
       <c r="H267" s="37"/>
       <c r="I267" s="1"/>
     </row>
-    <row r="268" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -8511,7 +8506,7 @@
       <c r="H268" s="37"/>
       <c r="I268" s="1"/>
     </row>
-    <row r="269" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -8520,7 +8515,7 @@
       <c r="H269" s="37"/>
       <c r="I269" s="1"/>
     </row>
-    <row r="270" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -8529,7 +8524,7 @@
       <c r="H270" s="37"/>
       <c r="I270" s="1"/>
     </row>
-    <row r="271" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -8538,7 +8533,7 @@
       <c r="H271" s="37"/>
       <c r="I271" s="1"/>
     </row>
-    <row r="272" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -8547,7 +8542,7 @@
       <c r="H272" s="37"/>
       <c r="I272" s="1"/>
     </row>
-    <row r="273" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -8556,7 +8551,7 @@
       <c r="H273" s="37"/>
       <c r="I273" s="1"/>
     </row>
-    <row r="274" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -8565,7 +8560,7 @@
       <c r="H274" s="37"/>
       <c r="I274" s="1"/>
     </row>
-    <row r="275" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -8574,7 +8569,7 @@
       <c r="H275" s="37"/>
       <c r="I275" s="1"/>
     </row>
-    <row r="276" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -8583,7 +8578,7 @@
       <c r="H276" s="37"/>
       <c r="I276" s="1"/>
     </row>
-    <row r="277" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -8592,7 +8587,7 @@
       <c r="H277" s="37"/>
       <c r="I277" s="1"/>
     </row>
-    <row r="278" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -8601,7 +8596,7 @@
       <c r="H278" s="37"/>
       <c r="I278" s="1"/>
     </row>
-    <row r="279" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -8610,7 +8605,7 @@
       <c r="H279" s="37"/>
       <c r="I279" s="1"/>
     </row>
-    <row r="280" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -8619,7 +8614,7 @@
       <c r="H280" s="37"/>
       <c r="I280" s="1"/>
     </row>
-    <row r="281" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -8628,7 +8623,7 @@
       <c r="H281" s="37"/>
       <c r="I281" s="1"/>
     </row>
-    <row r="282" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -8637,7 +8632,7 @@
       <c r="H282" s="37"/>
       <c r="I282" s="1"/>
     </row>
-    <row r="283" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -8646,7 +8641,7 @@
       <c r="H283" s="37"/>
       <c r="I283" s="1"/>
     </row>
-    <row r="284" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -8655,7 +8650,7 @@
       <c r="H284" s="37"/>
       <c r="I284" s="1"/>
     </row>
-    <row r="285" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -8664,7 +8659,7 @@
       <c r="H285" s="37"/>
       <c r="I285" s="1"/>
     </row>
-    <row r="286" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -8709,15 +8704,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B77D73-0EEE-4415-BB37-31865BBB2DB3}">
   <dimension ref="A1:C55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="34.33203125" style="72" customWidth="1"/>
-    <col min="3" max="3" width="49.33203125" style="72" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" style="72" customWidth="1"/>
+    <col min="3" max="3" width="49.28515625" style="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:3" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:3" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="73" t="s">
         <v>534</v>
       </c>
@@ -8728,7 +8723,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A3" s="76">
         <v>1</v>
       </c>
@@ -8739,7 +8734,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="76">
         <v>2</v>
       </c>
@@ -8750,7 +8745,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="76">
         <v>3</v>
       </c>
@@ -8761,7 +8756,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="76">
         <v>4</v>
       </c>
@@ -8772,7 +8767,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="76">
         <v>5</v>
       </c>
@@ -8783,7 +8778,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="76">
         <v>6</v>
       </c>
@@ -8794,7 +8789,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="76">
         <v>7</v>
       </c>
@@ -8805,7 +8800,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="76">
         <v>8</v>
       </c>
@@ -8816,7 +8811,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="76">
         <v>9</v>
       </c>
@@ -8827,7 +8822,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="76">
         <v>10</v>
       </c>
@@ -8838,7 +8833,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="76">
         <v>11</v>
       </c>
@@ -8849,7 +8844,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="69" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A14" s="76">
         <v>12</v>
       </c>
@@ -8860,7 +8855,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="76">
         <v>13</v>
       </c>
@@ -8871,7 +8866,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A16" s="76">
         <v>14</v>
       </c>
@@ -8882,7 +8877,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="69" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A17" s="76">
         <v>15</v>
       </c>
@@ -8893,7 +8888,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A18" s="76">
         <v>16</v>
       </c>
@@ -8904,7 +8899,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A19" s="76">
         <v>17</v>
       </c>
@@ -8915,7 +8910,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="76">
         <v>18</v>
       </c>
@@ -8924,7 +8919,7 @@
       </c>
       <c r="C20" s="77"/>
     </row>
-    <row r="21" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A21" s="76">
         <v>19</v>
       </c>
@@ -8935,7 +8930,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="76">
         <v>20</v>
       </c>
@@ -8946,7 +8941,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A23" s="76">
         <v>21</v>
       </c>
@@ -8957,7 +8952,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="76">
         <v>22</v>
       </c>
@@ -8966,7 +8961,7 @@
       </c>
       <c r="C24" s="77"/>
     </row>
-    <row r="25" spans="1:3" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A25" s="81">
         <v>23</v>
       </c>
@@ -8977,7 +8972,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="76">
         <v>24</v>
       </c>
@@ -8988,7 +8983,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A27" s="76">
         <v>25</v>
       </c>
@@ -8999,7 +8994,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A28" s="76">
         <v>26</v>
       </c>
@@ -9010,7 +9005,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="76">
         <v>27</v>
       </c>
@@ -9021,7 +9016,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="76">
         <v>28</v>
       </c>
@@ -9032,7 +9027,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="76">
         <v>29</v>
       </c>
@@ -9043,7 +9038,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A32" s="76">
         <v>30</v>
       </c>
@@ -9054,7 +9049,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="76">
         <v>31</v>
       </c>
@@ -9065,7 +9060,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" s="76">
         <v>32</v>
       </c>
@@ -9076,7 +9071,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" s="76">
         <v>33</v>
       </c>
@@ -9087,7 +9082,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" s="76">
         <v>34</v>
       </c>
@@ -9098,7 +9093,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="76">
         <v>35</v>
       </c>
@@ -9109,7 +9104,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A38" s="76">
         <v>36</v>
       </c>
@@ -9120,7 +9115,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="76">
         <v>37</v>
       </c>
@@ -9131,7 +9126,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="76">
         <v>38</v>
       </c>
@@ -9142,7 +9137,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A41" s="76">
         <v>39</v>
       </c>
@@ -9153,7 +9148,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="69" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A42" s="76">
         <v>40</v>
       </c>
@@ -9164,7 +9159,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="76">
         <v>41</v>
       </c>
@@ -9175,7 +9170,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="76">
         <v>42</v>
       </c>
@@ -9186,7 +9181,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="76">
         <v>43</v>
       </c>
@@ -9197,7 +9192,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="76">
         <v>44</v>
       </c>
@@ -9208,7 +9203,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="76">
         <v>45</v>
       </c>
@@ -9219,7 +9214,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A48" s="76">
         <v>46</v>
       </c>
@@ -9230,7 +9225,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49" s="76">
         <v>47</v>
       </c>
@@ -9241,7 +9236,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="51" x14ac:dyDescent="0.25">
       <c r="A50" s="76">
         <v>48</v>
       </c>
@@ -9252,7 +9247,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A51" s="76">
         <v>49</v>
       </c>
@@ -9263,7 +9258,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A52" s="76">
         <v>50</v>
       </c>
@@ -9274,7 +9269,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="76">
         <v>51</v>
       </c>
@@ -9283,7 +9278,7 @@
       </c>
       <c r="C53" s="83"/>
     </row>
-    <row r="54" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A54" s="76">
         <v>51</v>
       </c>
@@ -9294,7 +9289,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A55" s="76">
         <v>52</v>
       </c>
